--- a/Data/National Accounts/PSA-18REOD_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-18REOD_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DA6CB2-7245-419A-9C52-FA3EF4228912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E16643-BBAE-43D3-9460-532A5CD0F6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REOD" sheetId="1" r:id="rId1"/>
@@ -613,9 +613,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -623,6 +620,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23598,7 +23598,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -23608,7 +23608,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -23810,10 +23810,10 @@
         <v>695394.96861848608</v>
       </c>
       <c r="Z12" s="8">
-        <v>778048.08686080156</v>
+        <v>780353.86081433133</v>
       </c>
       <c r="AA12" s="8">
-        <v>843888.4885807134</v>
+        <v>846713.85084260534</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -23962,7 +23962,7 @@
         <v>674020.74370543764</v>
       </c>
       <c r="Z13" s="8">
-        <v>707829.13825305761</v>
+        <v>707831.80520200112</v>
       </c>
       <c r="AA13" s="8">
         <v>738251.48106701847</v>
@@ -24212,10 +24212,10 @@
         <v>1369415.7123239236</v>
       </c>
       <c r="Z15" s="11">
-        <v>1485877.2251138592</v>
+        <v>1488185.6660163323</v>
       </c>
       <c r="AA15" s="11">
-        <v>1582139.9696477319</v>
+        <v>1584965.3319096239</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -24529,7 +24529,7 @@
     </row>
     <row r="22" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:96" x14ac:dyDescent="0.2">
@@ -24539,7 +24539,7 @@
     </row>
     <row r="25" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:96" x14ac:dyDescent="0.2">
@@ -24741,10 +24741,10 @@
         <v>566243.75217096694</v>
       </c>
       <c r="Z31" s="8">
-        <v>611843.23812447756</v>
+        <v>613642.45939949201</v>
       </c>
       <c r="AA31" s="8">
-        <v>654018.07580010185</v>
+        <v>656224.40271030576</v>
       </c>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -24893,7 +24893,7 @@
         <v>585670.10475526319</v>
       </c>
       <c r="Z32" s="8">
-        <v>598608.37324987049</v>
+        <v>598610.60495705612</v>
       </c>
       <c r="AA32" s="8">
         <v>611157.22653977864</v>
@@ -25143,10 +25143,10 @@
         <v>1151913.8569262302</v>
       </c>
       <c r="Z34" s="11">
-        <v>1210451.6113743479</v>
+        <v>1212253.0643565482</v>
       </c>
       <c r="AA34" s="11">
-        <v>1265175.3023398805</v>
+        <v>1267381.6292500845</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -25460,7 +25460,7 @@
     </row>
     <row r="41" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:96" x14ac:dyDescent="0.2">
@@ -25470,7 +25470,7 @@
     </row>
     <row r="44" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:96" x14ac:dyDescent="0.2">
@@ -25586,7 +25586,7 @@
         <v>46</v>
       </c>
       <c r="Z48" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA48" s="16"/>
     </row>
@@ -25667,10 +25667,10 @@
         <v>12.522341891664553</v>
       </c>
       <c r="Y50" s="17">
-        <v>11.885780307919006</v>
+        <v>12.217357908790987</v>
       </c>
       <c r="Z50" s="17">
-        <v>8.4622535331406965</v>
+        <v>8.5038331147647028</v>
       </c>
       <c r="AA50" s="17"/>
       <c r="AB50" s="9"/>
@@ -25812,10 +25812,10 @@
         <v>7.1821660363895887</v>
       </c>
       <c r="Y51" s="17">
-        <v>5.0159279018265721</v>
+        <v>5.0163235794030214</v>
       </c>
       <c r="Z51" s="17">
-        <v>4.2979783071722721</v>
+        <v>4.2975853361571126</v>
       </c>
       <c r="AA51" s="17"/>
       <c r="AB51" s="9"/>
@@ -26050,10 +26050,10 @@
         <v>9.8290210119639738</v>
       </c>
       <c r="Y53" s="17">
-        <v>8.5044673974346381</v>
+        <v>8.6730386268793325</v>
       </c>
       <c r="Z53" s="17">
-        <v>6.4785126864365594</v>
+        <v>6.5031983645130254</v>
       </c>
       <c r="AA53" s="17"/>
       <c r="AB53" s="9"/>
@@ -26353,7 +26353,7 @@
     </row>
     <row r="60" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:91" x14ac:dyDescent="0.2">
@@ -26363,7 +26363,7 @@
     </row>
     <row r="63" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:91" x14ac:dyDescent="0.2">
@@ -26479,7 +26479,7 @@
         <v>46</v>
       </c>
       <c r="Z67" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA67" s="6"/>
     </row>
@@ -26560,10 +26560,10 @@
         <v>5.8944722654201911</v>
       </c>
       <c r="Y69" s="17">
-        <v>8.0529782057078876</v>
+        <v>8.3707249831542327</v>
       </c>
       <c r="Z69" s="17">
-        <v>6.8930789861967696</v>
+        <v>6.9392107176684306</v>
       </c>
       <c r="AA69" s="17"/>
       <c r="AB69" s="9"/>
@@ -26705,10 +26705,10 @@
         <v>2.1323530176427852</v>
       </c>
       <c r="Y70" s="17">
-        <v>2.2091393071896448</v>
+        <v>2.209520359110769</v>
       </c>
       <c r="Z70" s="17">
-        <v>2.0963377477965821</v>
+        <v>2.0959571178366616</v>
       </c>
       <c r="AA70" s="17"/>
       <c r="AB70" s="9"/>
@@ -26943,10 +26943,10 @@
         <v>3.9476911685827361</v>
       </c>
       <c r="Y72" s="17">
-        <v>5.0817822961449508</v>
+        <v>5.2381701172800774</v>
       </c>
       <c r="Z72" s="17">
-        <v>4.520931729224543</v>
+        <v>4.5476119231587973</v>
       </c>
       <c r="AA72" s="17"/>
       <c r="AB72" s="9"/>
@@ -27246,7 +27246,7 @@
     </row>
     <row r="78" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:96" x14ac:dyDescent="0.2">
@@ -27256,7 +27256,7 @@
     </row>
     <row r="81" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:96" x14ac:dyDescent="0.2">
@@ -27458,10 +27458,10 @@
         <v>122.80841350608391</v>
       </c>
       <c r="Z87" s="17">
-        <v>127.16461315251313</v>
+        <v>127.16751405663527</v>
       </c>
       <c r="AA87" s="17">
-        <v>129.03137081468751</v>
+        <v>129.02809577722948</v>
       </c>
       <c r="AB87" s="9"/>
       <c r="AC87" s="9"/>
@@ -27610,7 +27610,7 @@
         <v>115.08539333539893</v>
       </c>
       <c r="Z88" s="17">
-        <v>118.24577969235928</v>
+        <v>118.24578437810678</v>
       </c>
       <c r="AA88" s="17">
         <v>120.79567237498215</v>
@@ -27860,10 +27860,10 @@
         <v>118.88178131462676</v>
       </c>
       <c r="Z90" s="17">
-        <v>122.75395490008829</v>
+        <v>122.76196363390892</v>
       </c>
       <c r="AA90" s="17">
-        <v>125.05302361827965</v>
+        <v>125.05825359386462</v>
       </c>
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
@@ -27981,7 +27981,7 @@
     </row>
     <row r="97" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:96" x14ac:dyDescent="0.2">
@@ -27991,7 +27991,7 @@
     </row>
     <row r="100" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:96" x14ac:dyDescent="0.2">
@@ -28193,10 +28193,10 @@
         <v>50.780414037924835</v>
       </c>
       <c r="Z106" s="17">
-        <v>52.362878554867251</v>
+        <v>52.436593002755558</v>
       </c>
       <c r="AA106" s="17">
-        <v>53.338421680137927</v>
+        <v>53.421600699773897</v>
       </c>
       <c r="AB106" s="9"/>
       <c r="AC106" s="9"/>
@@ -28345,10 +28345,10 @@
         <v>49.219585962075172</v>
       </c>
       <c r="Z107" s="17">
-        <v>47.637121445132749</v>
+        <v>47.563406997244449</v>
       </c>
       <c r="AA107" s="17">
-        <v>46.661578319862073</v>
+        <v>46.578399300226096</v>
       </c>
       <c r="AB107" s="9"/>
       <c r="AC107" s="9"/>
@@ -28912,7 +28912,7 @@
     </row>
     <row r="116" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:96" x14ac:dyDescent="0.2">
@@ -28922,7 +28922,7 @@
     </row>
     <row r="119" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:96" x14ac:dyDescent="0.2">
@@ -29124,10 +29124,10 @@
         <v>49.156779282257538</v>
       </c>
       <c r="Z125" s="17">
-        <v>50.546691199806837</v>
+        <v>50.619996553706983</v>
       </c>
       <c r="AA125" s="17">
-        <v>51.693869979166294</v>
+        <v>51.777963919091739</v>
       </c>
       <c r="AB125" s="9"/>
       <c r="AC125" s="9"/>
@@ -29276,10 +29276,10 @@
         <v>50.84322071774244</v>
       </c>
       <c r="Z126" s="17">
-        <v>49.453308800193177</v>
+        <v>49.38000344629301</v>
       </c>
       <c r="AA126" s="17">
-        <v>48.306130020833713</v>
+        <v>48.222036080908254</v>
       </c>
       <c r="AB126" s="9"/>
       <c r="AC126" s="9"/>
